--- a/docs/REPAIR01_20260823/baseline_v1/11 · المراجعة الثانية.xlsx
+++ b/docs/REPAIR01_20260823/baseline_v1/11 · المراجعة الثانية.xlsx
@@ -74,7 +74,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">c8dc29a766acf8868fc9706a64afd79a56c4194d</t>
+          <t xml:space="preserve">f8b6da6ab5a24d3dabb6ae943a2a808955d66f3d</t>
         </is>
       </c>
     </row>
@@ -86,7 +86,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-27 00:52:12</t>
+          <t xml:space="preserve">2026-08-27 01:07:32</t>
         </is>
       </c>
     </row>
@@ -214,7 +214,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-27 03:52:11</t>
+          <t xml:space="preserve">2026-08-27 04:07:30</t>
         </is>
       </c>
     </row>
@@ -261,7 +261,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-27 03:52:11</t>
+          <t xml:space="preserve">2026-08-27 04:07:30</t>
         </is>
       </c>
     </row>
@@ -308,7 +308,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-27 03:52:11</t>
+          <t xml:space="preserve">2026-08-27 04:07:30</t>
         </is>
       </c>
     </row>
@@ -355,7 +355,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-27 03:52:11</t>
+          <t xml:space="preserve">2026-08-27 04:07:30</t>
         </is>
       </c>
     </row>
@@ -382,7 +382,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 من 113</t>
+          <t xml:space="preserve">0 من 114</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -397,12 +397,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t xml:space="preserve">قراءةُ 113 وثيقةً والبحثُ عن صيغةِ نسبةِ اكتمالٍ مجمَّعة</t>
+          <t xml:space="preserve">قراءةُ 114 وثيقةً والبحثُ عن صيغةِ نسبةِ اكتمالٍ مجمَّعة</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-27 03:52:11</t>
+          <t xml:space="preserve">2026-08-27 04:07:30</t>
         </is>
       </c>
     </row>
@@ -449,7 +449,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-27 03:52:11</t>
+          <t xml:space="preserve">2026-08-27 04:07:30</t>
         </is>
       </c>
     </row>
@@ -496,7 +496,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-27 03:52:11</t>
+          <t xml:space="preserve">2026-08-27 04:07:30</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-27 03:52:11</t>
+          <t xml:space="preserve">2026-08-27 04:07:30</t>
         </is>
       </c>
     </row>
@@ -590,7 +590,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-27 03:52:11</t>
+          <t xml:space="preserve">2026-08-27 04:07:30</t>
         </is>
       </c>
     </row>
@@ -637,7 +637,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-27 03:52:11</t>
+          <t xml:space="preserve">2026-08-27 04:07:30</t>
         </is>
       </c>
     </row>
@@ -684,7 +684,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-27 03:52:11</t>
+          <t xml:space="preserve">2026-08-27 04:07:30</t>
         </is>
       </c>
     </row>
@@ -731,7 +731,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-27 03:52:11</t>
+          <t xml:space="preserve">2026-08-27 04:07:30</t>
         </is>
       </c>
     </row>

--- a/docs/REPAIR01_20260823/baseline_v1/11 · المراجعة الثانية.xlsx
+++ b/docs/REPAIR01_20260823/baseline_v1/11 · المراجعة الثانية.xlsx
@@ -74,7 +74,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">f8b6da6ab5a24d3dabb6ae943a2a808955d66f3d</t>
+          <t xml:space="preserve">47577ee7f22d84fa3868337c2947b5e84db11951</t>
         </is>
       </c>
     </row>
@@ -86,7 +86,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-27 01:07:32</t>
+          <t xml:space="preserve">2026-08-27 01:16:52</t>
         </is>
       </c>
     </row>
@@ -214,7 +214,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-27 04:07:30</t>
+          <t xml:space="preserve">2026-08-27 04:16:50</t>
         </is>
       </c>
     </row>
@@ -261,7 +261,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-27 04:07:30</t>
+          <t xml:space="preserve">2026-08-27 04:16:50</t>
         </is>
       </c>
     </row>
@@ -308,7 +308,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-27 04:07:30</t>
+          <t xml:space="preserve">2026-08-27 04:16:50</t>
         </is>
       </c>
     </row>
@@ -355,7 +355,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-27 04:07:30</t>
+          <t xml:space="preserve">2026-08-27 04:16:50</t>
         </is>
       </c>
     </row>
@@ -402,7 +402,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-27 04:07:30</t>
+          <t xml:space="preserve">2026-08-27 04:16:50</t>
         </is>
       </c>
     </row>
@@ -449,7 +449,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-27 04:07:30</t>
+          <t xml:space="preserve">2026-08-27 04:16:50</t>
         </is>
       </c>
     </row>
@@ -496,7 +496,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-27 04:07:30</t>
+          <t xml:space="preserve">2026-08-27 04:16:50</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-27 04:07:30</t>
+          <t xml:space="preserve">2026-08-27 04:16:50</t>
         </is>
       </c>
     </row>
@@ -590,7 +590,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-27 04:07:30</t>
+          <t xml:space="preserve">2026-08-27 04:16:50</t>
         </is>
       </c>
     </row>
@@ -637,7 +637,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-27 04:07:30</t>
+          <t xml:space="preserve">2026-08-27 04:16:50</t>
         </is>
       </c>
     </row>
@@ -684,7 +684,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-27 04:07:30</t>
+          <t xml:space="preserve">2026-08-27 04:16:50</t>
         </is>
       </c>
     </row>
@@ -731,7 +731,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-27 04:07:30</t>
+          <t xml:space="preserve">2026-08-27 04:16:50</t>
         </is>
       </c>
     </row>

--- a/docs/REPAIR01_20260823/baseline_v1/11 · المراجعة الثانية.xlsx
+++ b/docs/REPAIR01_20260823/baseline_v1/11 · المراجعة الثانية.xlsx
@@ -74,7 +74,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">47577ee7f22d84fa3868337c2947b5e84db11951</t>
+          <t xml:space="preserve">9082e8cbf7d2c1288ba7458b99cf6b87a373d5ad</t>
         </is>
       </c>
     </row>
@@ -86,7 +86,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-27 01:16:52</t>
+          <t xml:space="preserve">2026-08-27 01:26:17</t>
         </is>
       </c>
     </row>

--- a/docs/REPAIR01_20260823/baseline_v1/11 · المراجعة الثانية.xlsx
+++ b/docs/REPAIR01_20260823/baseline_v1/11 · المراجعة الثانية.xlsx
@@ -74,7 +74,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">9082e8cbf7d2c1288ba7458b99cf6b87a373d5ad</t>
+          <t xml:space="preserve">05a0010b03fa63f30746693f8d0975301b1d7e49</t>
         </is>
       </c>
     </row>
@@ -86,7 +86,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-27 01:26:17</t>
+          <t xml:space="preserve">2026-08-27 01:31:08</t>
         </is>
       </c>
     </row>
